--- a/data/trans_camb/P57_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Clase-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 14,65</t>
+          <t>1,12; 15,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 21,92</t>
+          <t>9,1; 22,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 15,89</t>
+          <t>6,75; 15,88</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 46,13</t>
+          <t>2,83; 47,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,28; 77,87</t>
+          <t>24,58; 79,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,58; 50,76</t>
+          <t>18,26; 50,64</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 22,37</t>
+          <t>8,79; 22,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,94; 25,9</t>
+          <t>13,28; 25,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 22,57</t>
+          <t>12,85; 22,5</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,65; 76,45</t>
+          <t>22,34; 78,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,09; 120,81</t>
+          <t>46,11; 121,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,4; 86,64</t>
+          <t>41,52; 89,5</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 60,35</t>
+          <t>17,68; 59,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 23,82</t>
+          <t>5,52; 24,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 54,76</t>
+          <t>16,53; 56,93</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,46; 239,89</t>
+          <t>59,81; 234,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,9; 118,89</t>
+          <t>15,73; 124,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,83; 215,23</t>
+          <t>56,57; 227,36</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,22; 21,8</t>
+          <t>12,68; 21,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 13,99</t>
+          <t>-13,75; 14,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 16,52</t>
+          <t>-2,55; 16,89</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,14; 83,06</t>
+          <t>43,13; 83,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 47,25</t>
+          <t>-41,86; 47,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 58,34</t>
+          <t>-7,66; 59,46</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,44; 25,88</t>
+          <t>13,36; 25,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 16,54</t>
+          <t>4,21; 16,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 17,8</t>
+          <t>7,41; 18,1</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>50,69; 119,66</t>
+          <t>49,06; 118,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15,45; 100,86</t>
+          <t>22,63; 103,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35,44; 90,88</t>
+          <t>35,85; 91,46</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,92; 29,94</t>
+          <t>6,54; 30,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9,73; 18,49</t>
+          <t>9,72; 18,72</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11,5; 20,43</t>
+          <t>11,67; 20,19</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14,07; 74,76</t>
+          <t>13,44; 76,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32,37; 71,4</t>
+          <t>31,75; 71,88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34,1; 68,49</t>
+          <t>35,94; 67,52</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>15,87; 32,16</t>
+          <t>16,07; 33,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,18; 14,83</t>
+          <t>4,36; 15,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,06; 22,21</t>
+          <t>11,76; 22,04</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>51,19; 107,61</t>
+          <t>52,05; 111,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16,56; 57,48</t>
+          <t>16,61; 58,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>41,6; 78,22</t>
+          <t>40,47; 77,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,67</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,33</t>
+          <t>10,96</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 15,0</t>
+          <t>1,63; 13,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 22,05</t>
+          <t>8,49; 20,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 15,88</t>
+          <t>6,44; 15,7</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 47,59</t>
+          <t>4,16; 43,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,58; 79,4</t>
+          <t>23,25; 75,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,26; 50,64</t>
+          <t>17,53; 49,71</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15,51</t>
+          <t>16,12</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19,97</t>
+          <t>19,99</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>18,14</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 22,72</t>
+          <t>9,54; 23,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,28; 25,85</t>
+          <t>12,63; 25,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,85; 22,5</t>
+          <t>13,27; 22,1</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,34; 78,13</t>
+          <t>26,45; 83,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,11; 121,45</t>
+          <t>45,15; 120,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,52; 89,5</t>
+          <t>42,41; 85,46</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38,18</t>
+          <t>18,75</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>14,65</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33,55</t>
+          <t>17,38</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,68; 59,45</t>
+          <t>12,55; 24,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 24,03</t>
+          <t>5,51; 23,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,53; 56,93</t>
+          <t>12,34; 22,13</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>130,55%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119,15%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59,81; 234,62</t>
+          <t>38,95; 93,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,73; 124,46</t>
+          <t>17,62; 116,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56,57; 227,36</t>
+          <t>39,85; 85,04</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>12,67</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,92</t>
+          <t>15,26</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,68; 21,62</t>
+          <t>12,89; 21,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 14,2</t>
+          <t>7,96; 16,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 16,89</t>
+          <t>12,21; 18,46</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,13; 83,16</t>
+          <t>43,34; 81,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 47,67</t>
+          <t>23,64; 60,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 59,46</t>
+          <t>39,56; 66,95</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>19,41</t>
+          <t>17,52</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,53</t>
+          <t>14,76</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>15,58</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,36; 25,79</t>
+          <t>11,68; 23,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,79</t>
+          <t>10,81; 18,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 18,1</t>
+          <t>12,27; 18,99</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>49,06; 118,61</t>
+          <t>43,82; 104,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22,63; 103,12</t>
+          <t>50,07; 115,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35,85; 91,46</t>
+          <t>54,35; 98,13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19,01</t>
+          <t>18,41</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14,01</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15,76</t>
+          <t>15,54</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6,54; 30,87</t>
+          <t>6,02; 28,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9,72; 18,72</t>
+          <t>10,44; 19,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11,67; 20,19</t>
+          <t>11,13; 19,42</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13,44; 76,96</t>
+          <t>12,31; 68,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31,75; 71,88</t>
+          <t>35,0; 73,98</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35,94; 67,52</t>
+          <t>32,86; 64,94</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>20,47</t>
+          <t>16,07</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11,43</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15,81</t>
+          <t>15,36</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>16,07; 33,6</t>
+          <t>13,46; 18,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,36; 15,05</t>
+          <t>12,69; 16,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11,76; 22,04</t>
+          <t>13,79; 16,88</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>52,05; 111,68</t>
+          <t>42,98; 64,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16,61; 58,18</t>
+          <t>46,46; 67,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40,47; 77,66</t>
+          <t>47,44; 61,34</t>
         </is>
       </c>
     </row>
